--- a/Z_Docs/Z_AMC_update/amc_configuration_template_20260806_101119.xlsx
+++ b/Z_Docs/Z_AMC_update/amc_configuration_template_20260806_101119.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
   <si>
     <t>Facility Id</t>
   </si>
@@ -45,13 +45,16 @@
     <t>Yes/No</t>
   </si>
   <si>
+    <t>Active_AMC</t>
+  </si>
+  <si>
     <t>FAC/2025/44285</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>FP1</t>
+    <t>FP2</t>
   </si>
   <si>
     <t>Solar Panel, Inverter, Battary</t>
@@ -69,13 +72,13 @@
     <t>3 Years</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>No</t>
   </si>
   <si>
-    <t>FP2</t>
+    <t>FP1</t>
   </si>
   <si>
-    <t>No</t>
+    <t>Yes</t>
   </si>
   <si>
     <t>FAC/2025/44599</t>
@@ -622,7 +625,9 @@
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="27" width="13.571428571428571" customWidth="1"/>
+    <col min="10" max="10" width="13.571428571428571" customWidth="1"/>
+    <col min="11" max="11" width="21.142857142857142" customWidth="1"/>
+    <col min="12" max="27" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
@@ -656,7 +661,9 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
@@ -674,38 +681,40 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" ht="42" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4">
         <v>6578767326</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
-      <c r="K2" s="3"/>
+      <c r="K2" s="3">
+        <v>3</v>
+      </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -723,38 +732,40 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" ht="42" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" ht="45" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="4">
         <v>6578767326</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>3</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -774,36 +785,38 @@
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4">
         <v>3317116311</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -823,36 +836,38 @@
     </row>
     <row r="5" ht="38.25" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4">
         <v>1111426431</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -872,36 +887,38 @@
     </row>
     <row r="6" ht="57" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4">
         <v>3574724674</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -921,36 +938,38 @@
     </row>
     <row r="7" ht="46.5" customHeight="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="4">
         <v>1111426670</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>13</v>
+      <c r="K7" s="3">
+        <v>0</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -15497,16 +15516,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>5</v>
@@ -15514,87 +15533,87 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>43</v>
+      <c r="C3" s="8" t="s">
+        <v>46</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>44</v>
+      <c r="D3" s="8" t="s">
+        <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>40</v>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
       </c>
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>45</v>
+      <c r="B4" s="8" t="s">
+        <v>42</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>47</v>
+      <c r="D4" s="8" t="s">
+        <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>40</v>
+      <c r="E4" s="8" t="s">
+        <v>50</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>45</v>
+      <c r="B5" s="8" t="s">
+        <v>42</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>48</v>
+      <c r="C5" s="8" t="s">
+        <v>46</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>49</v>
+      <c r="D5" s="8" t="s">
+        <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>40</v>
+      <c r="E5" s="8" t="s">
+        <v>52</v>
       </c>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="B6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -15614,27 +15633,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
